--- a/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ismaël a joué avec les cubes. Il a chaud. Sa langue est sèche. Il a soif. Papa est dans la cuisine. Ismaël dit : j'ai soif, papa. Papa sourit. Papa prend un verre. Il verse de l'eau. L'eau chante dans le verre. Ismaël prend le verre d'eau. Il boit une gorgée. C'est frais. Il boit encore. Papa dit : quand on a soif, on boit de l'eau. Dans un verre. Ismaël pose le verre. Il se sent mieux. Il touche le verre. Le verre est lisse. Papa essuie une goutte. Ismaël sourit.</t>
+          <t>Ismaël a joué avec les cubes. Il a chaud. Sa langue est sèche. Il a soif. Papa est dans la cuisine. J'ai soif, papa. Papa sourit. Papa prend un verre. Il verse de l'eau. L'eau chante dans le verre. Ismaël prend le verre d'eau. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Ismaël pose le verre. Il se sent mieux. Il touche le verre. Le verre est lisse. Papa essuie une goutte. Ismaël sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ismaël a joué avec les cubes. Il a chaud. Sa langue est sèche. Il a soif. Papa est dans la cuisine.
+enfant-m|J'ai soif, papa. Papa sourit. Papa prend un verre. Il verse de l'eau. L'eau chante dans le verre.
+narrateur|Ismaël prend le verre d'eau. Il boit une gorgée. C'est frais. Il boit encore.
+papa|Quand on a soif, on boit de l'eau.
+narrateur|Dans un verre. Ismaël pose le verre. Il se sent mieux. Il touche le verre. Le verre est lisse. Papa essuie une goutte. Ismaël sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ismaël a soif. Que prend-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ismaël avait soif. Il a pris le verre. Il a bu de l'eau. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ismaël retourne aux cubes. Le verre reste près de l'évier.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Dans un verre. Ismaël pose le verre. Il se sent mieux. Il touche le verre. Le verre est lisse. Papa essuie une goutte. Ismaël sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Ismaël a soif. Que prend-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Ismaël avait soif. Il a pris le verre. Il a bu de l'eau. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Ismaël retourne aux cubes. Le verre reste près de l'évier.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ismaël boit un verre d'eau</t>
+          <t>Le cube rouge et le verre</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un cube rouge roule jusqu'au tapis. La tour penche. Raphaël a chaud. Papa verse de l'eau. Il boit dans un verre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ismaël a joué avec les cubes. Il a chaud. Sa langue est sèche. Il a soif. Papa est dans la cuisine. J'ai soif, papa. Papa sourit. Papa prend un verre. Il verse de l'eau. L'eau chante dans le verre. Ismaël prend le verre d'eau. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Ismaël pose le verre. Il se sent mieux. Il touche le verre. Le verre est lisse. Papa essuie une goutte. Ismaël sourit.</t>
+          <t>Un cube rouge roule jusqu'au tapis. Le tapis est épais, tout doux. La tour penche un peu. Le salon est tiède. Un rayon touche le bois du plancher. Raphaël habite ici, avec papa. Maman plie une serviette, tout près. Les cubes sont en bois. Tu as vu le cube rouge, Raphaël ? Il a roulé, papa. Oui. On le pose près de la tour ? Oui, papa. Raphaël pose le cube. Le bois est lisse sous ses doigts. En ce moment, Raphaël a chaud. Ses joues sont chaudes. Sa langue est sèche. J'ai soif, papa. On va à la cuisine ? Oui. Ils vont dans la cuisine. Le carrelage est frais sous les pieds. Viens. On prend un verre. Papa prend un verre. Il verse de l'eau. L'eau chante dans le verre. Tu prends le verre d'eau ? Raphaël prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Raphaël pose le verre. Tu te sens mieux ? Oui, papa. Bravo, Raphaël. Tu as bu de l'eau. Il touche le verre. Le verre est lisse. Tu as vu une goutte ? Oui. Elle glisse. Tu restes près de la table ? Oui, papa. On est bien, ici. Le carrelage est encore frais. Raphaël tient le verre à deux mains. Tes joues sont moins chaudes, hein ? Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ismaël a joué avec les cubes. Il a chaud. Sa langue est sèche. Il a soif. Papa est dans la cuisine.
-enfant-m|J'ai soif, papa. Papa sourit. Papa prend un verre. Il verse de l'eau. L'eau chante dans le verre.
-narrateur|Ismaël prend le verre d'eau. Il boit une gorgée. C'est frais. Il boit encore.
+          <t>narrateur|Un cube rouge roule jusqu'au tapis.
+narrateur|Le tapis est épais, tout doux.
+narrateur|La tour penche un peu.
+narrateur|Le salon est tiède.
+narrateur|Un rayon touche le bois du plancher.
+narrateur|Raphaël habite ici, avec papa.
+narrateur|Maman plie une serviette, tout près.
+narrateur|Les cubes sont en bois.
+papa|Tu as vu le cube rouge, Raphaël ?
+enfant-m|Il a roulé, papa.
+papa|Oui.
+papa|On le pose près de la tour ?
+enfant-m|Oui, papa.
+narrateur|Raphaël pose le cube.
+narrateur|Le bois est lisse sous ses doigts.
+narrateur|En ce moment, Raphaël a chaud.
+narrateur|Ses joues sont chaudes.
+narrateur|Sa langue est sèche.
+enfant-m|J'ai soif, papa.
+papa|On va à la cuisine ?
+enfant-m|Oui.
+narrateur|Ils vont dans la cuisine.
+narrateur|Le carrelage est frais sous les pieds.
+papa|Viens.
+papa|On prend un verre.
+narrateur|Papa prend un verre.
+narrateur|Il verse de l'eau.
+narrateur|L'eau chante dans le verre.
+papa|Tu prends le verre d'eau ?
+narrateur|Raphaël prend le verre.
+narrateur|Il boit une gorgée.
+narrateur|C'est frais.
+narrateur|Il boit encore.
 papa|Quand on a soif, on boit de l'eau.
-narrateur|Dans un verre. Ismaël pose le verre. Il se sent mieux. Il touche le verre. Le verre est lisse. Papa essuie une goutte. Ismaël sourit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Dans un verre.
+narrateur|Raphaël pose le verre.
+papa|Tu te sens mieux ?
+enfant-m|Oui, papa.
+papa|Bravo, Raphaël.
+papa|Tu as bu de l'eau.
+narrateur|Il touche le verre.
+narrateur|Le verre est lisse.
+papa|Tu as vu une goutte ?
+enfant-m|Oui.
+enfant-m|Elle glisse.
+papa|Tu restes près de la table ?
+enfant-m|Oui, papa.
+papa|On est bien, ici.
+narrateur|Le carrelage est encore frais.
+narrateur|Raphaël tient le verre à deux mains.
+papa|Tes joues sont moins chaudes, hein ?
+enfant-m|Oui.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cubes,verre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ismaël a soif. Que prend-il ?</t>
+          <t>Raphaël a soif. Que prend-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ismaël a soif. Que prend-il ?</t>
+          <t>narrateur|Raphaël a soif.
+narrateur|Que prend-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ismaël avait soif. Il a pris le verre. Il a bu de l'eau. Papa était là.</t>
+          <t>Raphaël avait soif. Il a pris le verre. Il a bu de l'eau. Bravo. C'est du bon travail. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Raphaël boit encore un peu. Il pose le verre. Le verre reste près de l'évier ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1745,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ismaël avait soif. Il a pris le verre. Il a bu de l'eau. Papa était là.</t>
+          <t>narrateur|Raphaël avait soif.
+narrateur|Il a pris le verre.
+narrateur|Il a bu de l'eau.
+papa|Bravo.
+papa|C'est du bon travail.
+enfant-m|C'est frais, papa.
+papa|Oui. L'eau est fraîche.
+papa|Tu veux encore une gorgée ?
+enfant-m|Oui.
+narrateur|Raphaël boit encore un peu.
+narrateur|Il pose le verre.
+papa|Le verre reste près de l'évier ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ismaël retourne aux cubes. Le verre reste près de l'évier.</t>
+          <t>On retourne aux cubes ? Oui, papa. Raphaël prend la main de papa. Le verre reste près de l'évier. Tu as fini de poser le verre ? Oui. Bravo. Au salon, la tour attend. Le cube rouge est à sa place. La tour penche encore, hein ? Un peu. On la tient ensemble ? Oui. Merci, papa. Merci, Raphaël. On reste un moment près des cubes ? Oui. Raphaël reste près de papa. La tour tient, maintenant ? Oui, papa. Bravo. Le tapis est doux sous les genoux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1925,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ismaël retourne aux cubes. Le verre reste près de l'évier.</t>
+          <t>papa|On retourne aux cubes ?
+enfant-m|Oui, papa.
+narrateur|Raphaël prend la main de papa.
+narrateur|Le verre reste près de l'évier.
+papa|Tu as fini de poser le verre ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Au salon, la tour attend.
+narrateur|Le cube rouge est à sa place.
+papa|La tour penche encore, hein ?
+enfant-m|Un peu.
+papa|On la tient ensemble ?
+enfant-m|Oui.
+enfant-m|Merci, papa.
+papa|Merci, Raphaël.
+papa|On reste un moment près des cubes ?
+enfant-m|Oui.
+narrateur|Raphaël reste près de papa.
+papa|La tour tient, maintenant ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Le tapis est doux sous les genoux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1974,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Raphaël. Tu as fait du bon travail. Le cube rouge reste près de la tour. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2114,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'avais soif.
+enfant-m|J'ai bu de l'eau.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Le cube rouge reste près de la tour.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2179,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ismaël a joué avec les cubes. Il a chaud. Sa langue est sèche. Il a soif. Papa est dans la cuisine. Ismaël dit : j'ai soif, papa. Papa sourit. Papa prend un verre. Il verse de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. L'eau chante dans le verre. Ismaël prend le verre d'eau. Il boit une gorgée. C'est frais. Il boit encore. Papa dit : quand on a soif, on boit de l'eau. Dans un verre. Ismaël pose le verre. Il se sent mieux. Il touche le verre. Le verre est lisse. Papa essuie une goutte. Ismaël sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un cube rouge roule jusqu'au tapis. Le tapis est épais, tout doux. La tour penche un peu. Le salon est tiède. Un rayon touche le bois du plancher. Raphaël habite ici, avec papa. Maman plie une serviette, tout près. Les cubes sont en bois. Tu as vu le cube rouge, Raphaël ? Il a roulé, papa. Oui. On le pose près de la tour ? Oui, papa. Raphaël pose le cube. Le bois est lisse sous ses doigts. En ce moment, Raphaël a chaud. Ses joues sont chaudes. Sa langue est sèche. J'ai soif, papa. On va à la cuisine ? Oui. Ils vont dans la cuisine. Le carrelage est frais sous les pieds. Viens. On prend un verre. Papa prend un verre. Il verse de l'eau. L'eau chante dans le verre. Tu prends le verre d'eau ? Raphaël prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Raphaël pose le verre. Tu te sens mieux ? Oui, papa. Bravo, Raphaël. Tu as bu de l'eau. Il touche le verre. Le verre est lisse. Tu as vu une goutte ? Oui. Elle glisse. Tu restes près de la table ? Oui, papa. On est bien, ici. Le carrelage est encore frais. Raphaël tient le verre à deux mains. Tes joues sont moins chaudes, hein ? Oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ismaël a &lt;emphasis level="moderate"&gt;soif&lt;/emphasis&gt;. Que prend-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a soif. Que prend-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1576,6 @@
 narrateur|Que prend-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël avait soif. Il a pris le verre. Il a bu de l'eau. Bravo. C'est du bon travail. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Raphaël boit encore un peu. Il pose le verre. Le verre reste près de l'évier ? Oui, papa.</t>
+          <t>Raphaël avait soif. Il a pris le verre. Il a bu de l'eau. Bravo. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Raphaël boit encore un peu. Il pose le verre. Le verre reste près de l'évier ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ismaël avait soif. Il a pris le verre. Il a bu de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël avait soif. Il a pris le verre. Il a bu de l'eau. Bravo. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Raphaël boit encore un peu. Il pose le verre. Le verre reste près de l'évier ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,7 +1748,6 @@
 narrateur|Il a pris le verre.
 narrateur|Il a bu de l'eau.
 papa|Bravo.
-papa|C'est du bon travail.
 enfant-m|C'est frais, papa.
 papa|Oui. L'eau est fraîche.
 papa|Tu veux encore une gorgée ?
@@ -1760,7 +1758,6 @@
 enfant-m|Oui, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ismaël retourne aux cubes. Le &lt;emphasis level="moderate"&gt;verre&lt;/emphasis&gt; reste près de l'évier.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On retourne aux cubes ? Oui, papa. Raphaël prend la main de papa. Le verre reste près de l'évier. Tu as fini de poser le verre ? Oui. Bravo. Au salon, la tour attend. Le cube rouge est à sa place. La tour penche encore, hein ? Un peu. On la tient ensemble ? Oui. Merci, papa. Merci, Raphaël. On reste un moment près des cubes ? Oui. Raphaël reste près de papa. La tour tient, maintenant ? Oui, papa. Bravo. Le tapis est doux sous les genoux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,7 +1946,6 @@
 narrateur|Le tapis est doux sous les genoux.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1974,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais soif. J'ai bu de l'eau. Bravo, Raphaël. Tu as fait du bon travail. Le cube rouge reste près de la tour. L'histoire est finie.</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Raphaël. Le cube rouge reste près de la tour.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Raphaël. Le cube rouge reste près de la tour.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2117,12 +2113,9 @@
           <t>enfant-m|J'avais soif.
 enfant-m|J'ai bu de l'eau.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
-narrateur|Le cube rouge reste près de la tour.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le cube rouge reste près de la tour.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2141,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2179,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-03.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>salon puis cuisine</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ismaël, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
